--- a/05_Figures/F06_prediction/proteins/trajectory/d_fcsa_I/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/trajectory/d_fcsa_I/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -131,43 +131,73 @@
     <t xml:space="preserve">EIF3F@T2</t>
   </si>
   <si>
+    <t xml:space="preserve">PPP1R2@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSMB5@T3</t>
   </si>
   <si>
     <t xml:space="preserve">RPL17@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">PPP1R2@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">SEC23A@T2</t>
   </si>
   <si>
+    <t xml:space="preserve">AIMP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLEC@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD23B@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPPL2A@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBB2A@T2</t>
+  </si>
+  <si>
     <t xml:space="preserve">CACNG1@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">MLEC@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP2@T2</t>
+    <t xml:space="preserve">CAPZB@T3</t>
   </si>
   <si>
     <t xml:space="preserve">HNRNPK@T1</t>
   </si>
   <si>
+    <t xml:space="preserve">MYH3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGM2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZYX@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMT1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUL@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS18B@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">SLC25A3@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">SPPL2A@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBB2A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMT1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPZB@T3</t>
+    <t xml:space="preserve">TMEM11@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLVRA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1I2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHDC3@T1</t>
   </si>
   <si>
     <t xml:space="preserve">LUM@T1</t>
@@ -176,366 +206,375 @@
     <t xml:space="preserve">MAP2K2@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">MRPS18B@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD23B@T3</t>
+    <t xml:space="preserve">MYBPC2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NARS1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGLY1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC44A2@T2</t>
   </si>
   <si>
     <t xml:space="preserve">SRSF2@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">TGM2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM11@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZYX@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLVRA@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">BPNT1@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">DCTN2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAB1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSCN1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K2@T2</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHMP2A@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">DYNC1I2@T3</t>
+    <t xml:space="preserve">FECH@T3</t>
   </si>
   <si>
     <t xml:space="preserve">GDI2@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">GLUL@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYBPC2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NARS1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGLY1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAB1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC44A2@T2</t>
+    <t xml:space="preserve">CAPZA2@T3</t>
   </si>
   <si>
     <t xml:space="preserve">CDNF@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">ECHDC3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECH@T3</t>
+    <t xml:space="preserve">CRIP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPX1@T3</t>
   </si>
   <si>
     <t xml:space="preserve">HDHD2@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">CAPZA2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUSP3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPX1@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">LYPLA2@T1</t>
   </si>
   <si>
+    <t xml:space="preserve">RPL13A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCDC43@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5B@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMPCB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC44A2@T1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ZYX@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">AKR1C1@T1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ANXA3@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">CAMK2A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FSCN1@T2</t>
+    <t xml:space="preserve">CAMK2G@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCXR@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HADHA@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LACTB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPK1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH14@T1</t>
   </si>
   <si>
     <t xml:space="preserve">PARVA@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">PMPCB@T3</t>
+    <t xml:space="preserve">UBE2M@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USP15@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCB7@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTN4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APEH@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOBEC2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGAP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPH@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1A3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROX@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BZW2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNA1S@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFL2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIC6@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ10A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAD1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7B@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJB1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLL1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2S3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3L@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF4A2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDOD1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPHX1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGIC1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERP29@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDC2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLO1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GORASP2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPX1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HK1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-DRA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPC@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSD17B12@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSD17B4@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPA2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IARS1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDI1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARS1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIF5B@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMC1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN2C1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP3K20@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBNL1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METAP2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METAP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGLL@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL12@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL22@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS27@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYBPH@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAPRT@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAB1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIPSNAP2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NME2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUDT2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPA3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA2G4@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCBP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCD6IP@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCD6IP@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFDN2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKM@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKG1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPID@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1R1A@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP5C@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAR2A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA2@T3</t>
   </si>
   <si>
     <t xml:space="preserve">PSMB2@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">RPL13A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC44A2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2G@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRIP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCXR@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF5B@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPT@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LACTB@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPK1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH14@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAB1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R1A@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2M@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USP15@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTN4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA11@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASPH@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATXN10@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BROX@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNB3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCDC43@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFL2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHCHD10@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ10A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7B@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJB1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLL1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3B@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3G@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3G@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3L@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF4A2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENDOD1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPHX1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGIC1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERP29@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUNDC2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLO1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMPR@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPS1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPX1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HADHA@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DRA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPC@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSD17B12@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSD17B4@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IARS1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KARS1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIF5B@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDHB@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN2C1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP1LC3B2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP3K20@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPK12@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METAP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGLL@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL12@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL22@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS27@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTIF2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYBPH@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAPRT@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIPSNAP2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDT2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA2G4@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCBP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6IP@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6IP@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFDN2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFKM@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHKG1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP5C@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAR2A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA2@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">PURA@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">RAB1A@T1</t>
-  </si>
-  <si>
     <t xml:space="preserve">RAB8A@T2</t>
   </si>
   <si>
     <t xml:space="preserve">RPA3@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">RPL10A@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">RPL12@T3</t>
   </si>
   <si>
@@ -545,6 +584,9 @@
     <t xml:space="preserve">RPL18A@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">RPL23A@T2</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPL4@T3</t>
   </si>
   <si>
@@ -554,7 +596,7 @@
     <t xml:space="preserve">RPL7A@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">RRAGC@T1</t>
+    <t xml:space="preserve">RPL9@T1</t>
   </si>
   <si>
     <t xml:space="preserve">RUVBL1@T1</t>
@@ -569,15 +611,21 @@
     <t xml:space="preserve">RWDD1@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">RYR1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHC@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHD@T1</t>
+  </si>
+  <si>
     <t xml:space="preserve">SNRPD3@T1</t>
   </si>
   <si>
     <t xml:space="preserve">SNX5@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">SPTBN1@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">STIM1@T2</t>
   </si>
   <si>
@@ -587,10 +635,7 @@
     <t xml:space="preserve">TARDBP@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">TNPO3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPP2@T2</t>
+    <t xml:space="preserve">TMX4@T3</t>
   </si>
   <si>
     <t xml:space="preserve">TTC38@T3</t>
@@ -603,6 +648,9 @@
   </si>
   <si>
     <t xml:space="preserve">WDR1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YWHAQ@T2</t>
   </si>
 </sst>
 </file>
@@ -989,16 +1037,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.298379640641116</v>
+        <v>-0.28426799925868</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0769230769230769</v>
+        <v>-0.112087912087912</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1022,29 +1070,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.298379640641116</v>
+        <v>-0.28426799925868</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0769230769230769</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.228855721393035</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.358208955223881</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.696212596135125</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.623856434295874</v>
-      </c>
+        <v>-0.112087912087912</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1068,2206 +1108,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.867628609404505</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.926400355981026</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.500270083944624</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.799773561675491</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.967144741508412</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.351178512749084</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.0518721541756224</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.927642380043848</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.01968667253579</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.59315167033718</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.0244451177064258</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.318513200641701</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.28135712052933</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.670501027623061</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.655635585216998</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.114640615574143</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.120290888876466</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.877045575953218</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.366742500437908</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.906366604249848</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.274249551920241</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-1.10920106729606</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.312616896477323</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.86009652944152</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.665354609285494</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.823206660694972</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.28450248275263</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.283549856017192</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.865274162874427</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-1.3665096871191</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.897358285480503</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.401011264559921</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.85691154737121</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.972196185151763</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.645687586556587</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.423544934148302</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.760469047830232</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.0394621264332975</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-1.79062389460324</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.671776222695013</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.95546223714443</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.27494185113468</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.719936791799571</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.312295801940808</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.13239525117951</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-1.39106403289444</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.570272450623791</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.996724888242786</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.460433803617514</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.607324002465748</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.396696930627429</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.120816946992161</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-1.44521479176145</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-1.82906269178082</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.406928872998614</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.486274112323599</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.16117186969207</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-1.56637740540901</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.932584771682004</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.541362977176922</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.458094779057925</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.421956179152715</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.587812272889849</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.115592495868335</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-1.8127161379494</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-1.17336789385006</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.649587082191986</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.949249509797719</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.471221671930487</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.346989893306199</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.879223166204987</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.02475372725474</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0.476868493813069</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.0648397306067596</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0.679654461747296</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.520595463276956</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.249969930884601</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-1.19865849895877</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.911684836150588</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-1.75712554812273</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.902557088098357</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.553299619105311</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.222281719454576</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.651631088568322</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.188121264935694</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-1.10502587219587</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.575492784248441</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.114715317710183</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.721248682835443</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-1.10444113938689</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.28916029854434</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.450803161816578</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.46489852713267</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.522448869047621</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-1.23567267475221</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.410459058964638</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.531558616258825</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.498345682206353</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.567232883731066</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.608301094412059</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.440030322558</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.694772841266242</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>0.044937219777641</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.908018910936439</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-2.26742170338685</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-4.02127246955576</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.188887808182276</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.715902777095663</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.33269624254674</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.401521403275047</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.353829353261795</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.221612449828213</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.353837875836343</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-1.25184087249536</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.0638159824198872</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.802582495924414</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.548898154186735</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.74258908038791</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.84586458585501</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-1.35573124031133</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-1.09295464190559</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0.148961935006356</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>0.0419719971875427</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.802843897777622</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-1.16054627697839</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-1.32333773221499</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.575844310231954</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.329640874385483</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>0.443633301934797</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-1.52212424241346</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.123222390746293</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.149209931130477</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.97477516636832</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.40909975723752</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.644267179406584</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.434375180065742</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.742713741243207</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.446995039573188</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-1.60289914343535</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-1.18084929407378</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.4661064335101</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.128107734067146</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.5009565048227</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.650278698187325</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.260894945767377</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-1.30731391164073</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.429112677184201</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.939420490014745</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.282231678231532</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>0.748240151844435</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.27089649364418</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.641719591405313</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.436266475406302</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.590809163614626</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.48473600202746</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.864427733829084</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-1.07348646756353</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.310525169462496</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-1.42424933256672</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.959268635084256</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0.509582232143954</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.414279027684229</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.988031620847211</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.0703877340107717</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.301026737555169</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.914078198973375</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>0.607094184188302</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-1.21150950203973</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-1.04008774753791</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.105501568805219</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.32122954748492</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.840032314512907</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.343261804144481</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.545743688160878</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>0.390753091245768</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-1.57945004569619</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.21830725149437</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-1.71613565144683</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.304572837023739</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0.19500038230033</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.56921409503657</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-1.38377886854036</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.159388482239547</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.259670277109535</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-1.48334911859848</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.481915487643533</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.32411701109857</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.798618016028824</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.340579534341249</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.565452386425718</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.544492703095367</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-1.26458047147725</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>0.085926556916905</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-1.04356330479925</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-1.01220266889678</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-1.92708086059173</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.833618215138016</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-2.11833545044448</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.353929774986065</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.498580916555545</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3310,7 +1150,7 @@
         <v>874.31</v>
       </c>
       <c r="E2" t="n">
-        <v>-581.454568255717</v>
+        <v>-509.189968838399</v>
       </c>
     </row>
     <row r="3">
@@ -3327,7 +1167,7 @@
         <v>1757.71</v>
       </c>
       <c r="E3" t="n">
-        <v>-216.402259877633</v>
+        <v>-355.516982336624</v>
       </c>
     </row>
     <row r="4">
@@ -3344,7 +1184,7 @@
         <v>1924.77</v>
       </c>
       <c r="E4" t="n">
-        <v>-142.07058499883</v>
+        <v>-223.340145831068</v>
       </c>
     </row>
     <row r="5">
@@ -3361,7 +1201,7 @@
         <v>274.62</v>
       </c>
       <c r="E5" t="n">
-        <v>-1100.77565037714</v>
+        <v>-1004.09696574588</v>
       </c>
     </row>
     <row r="6">
@@ -3378,7 +1218,7 @@
         <v>545.54</v>
       </c>
       <c r="E6" t="n">
-        <v>-197.406666310457</v>
+        <v>-30.0909889936059</v>
       </c>
     </row>
     <row r="7">
@@ -3395,7 +1235,7 @@
         <v>1276.8</v>
       </c>
       <c r="E7" t="n">
-        <v>-55.6919246242906</v>
+        <v>-289.0863702639</v>
       </c>
     </row>
     <row r="8">
@@ -3412,7 +1252,7 @@
         <v>171.549999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>465.685132878208</v>
+        <v>436.593527842282</v>
       </c>
     </row>
     <row r="9">
@@ -3429,7 +1269,7 @@
         <v>621.64</v>
       </c>
       <c r="E9" t="n">
-        <v>1672.5680045728</v>
+        <v>1640.80514751959</v>
       </c>
     </row>
     <row r="10">
@@ -3446,7 +1286,7 @@
         <v>-1588.06</v>
       </c>
       <c r="E10" t="n">
-        <v>200.402960302277</v>
+        <v>150.961206209695</v>
       </c>
     </row>
     <row r="11">
@@ -3463,7 +1303,7 @@
         <v>-845.39</v>
       </c>
       <c r="E11" t="n">
-        <v>-1306.86600648003</v>
+        <v>-878.283517048996</v>
       </c>
     </row>
     <row r="12">
@@ -3480,7 +1320,7 @@
         <v>-2646.36</v>
       </c>
       <c r="E12" t="n">
-        <v>438.919621727169</v>
+        <v>302.520945505047</v>
       </c>
     </row>
     <row r="13">
@@ -3497,7 +1337,7 @@
         <v>-1385.12</v>
       </c>
       <c r="E13" t="n">
-        <v>-1541.23408912653</v>
+        <v>-1543.78284135132</v>
       </c>
     </row>
     <row r="14">
@@ -3514,7 +1354,7 @@
         <v>-2594.04</v>
       </c>
       <c r="E14" t="n">
-        <v>524.123002889527</v>
+        <v>551.073524276211</v>
       </c>
     </row>
     <row r="15">
@@ -3531,7 +1371,7 @@
         <v>-1268.92</v>
       </c>
       <c r="E15" t="n">
-        <v>-1919.08271294412</v>
+        <v>-1735.33637721562</v>
       </c>
     </row>
   </sheetData>
@@ -3624,10 +1464,10 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.928571428571429</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3658,10 +1498,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="8">
@@ -3692,10 +1532,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="10">
@@ -3709,10 +1549,10 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="11">
@@ -3726,10 +1566,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="12">
@@ -3777,10 +1617,10 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="15">
@@ -3794,10 +1634,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="16">
@@ -3811,10 +1651,10 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="17">
@@ -3828,10 +1668,10 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="18">
@@ -3930,10 +1770,10 @@
         <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="24">
@@ -4100,10 +1940,10 @@
         <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
@@ -4134,10 +1974,10 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>0.428571428571429</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -4168,10 +2008,10 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>0.357142857142857</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="38">
@@ -4321,10 +2161,10 @@
         <v>81</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="47">
@@ -4338,10 +2178,10 @@
         <v>82</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="48">
@@ -4355,10 +2195,10 @@
         <v>83</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="49">
@@ -4457,10 +2297,10 @@
         <v>89</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="55">
@@ -4474,10 +2314,10 @@
         <v>90</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="56">
@@ -6262,6 +4102,278 @@
         <v>1</v>
       </c>
       <c r="E160" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="s">
+        <v>196</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="s">
+        <v>197</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="s">
+        <v>198</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="s">
+        <v>199</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="s">
+        <v>200</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="s">
+        <v>201</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="s">
+        <v>202</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="s">
+        <v>203</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="s">
+        <v>204</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="s">
+        <v>205</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="s">
+        <v>206</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="s">
+        <v>207</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="s">
+        <v>208</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="s">
+        <v>209</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="s">
+        <v>210</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="s">
+        <v>211</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/trajectory/d_fcsa_I/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/trajectory/d_fcsa_I/spls/c_data/results.xlsx
@@ -1073,7 +1073,7 @@
         <v>5696</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.28426799925868</v>
@@ -1081,10 +1081,18 @@
       <c r="I3" t="n">
         <v>-0.112087912087912</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.233830845771144</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.437810945273632</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.67860119650498</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.608666835016733</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1108,6 +1116,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.897739302313609</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.900854679552358</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.526944924862057</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.629429636195444</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.799536674444948</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.421758764768348</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.37025625703823</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.818778500136101</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.912518479249897</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.58418065928508</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.0563653313578569</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.329918790402092</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.18191366464842</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.580771667805302</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.632741639339839</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.0908761607953934</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.139204630783967</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.894720857179495</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.259352771901618</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.726368413776778</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.128603129795211</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.823126650838107</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.170383988928143</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.930964952916787</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.704737023487134</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.734309884815953</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.32410596544678</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.193803914054168</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.828939238602039</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.22912040023786</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.992418481662423</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.589106112619584</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.20792635240518</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.981137530697974</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.596768891398208</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.421802768907585</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.759780284869286</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.0519915670710283</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.681154253205668</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.679304415072322</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-2.27920667473542</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.12426969278523</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.631992801559842</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.33684251716832</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.12541108465131</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.804096042461012</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.774994198456265</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.795260236879156</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.40919313233227</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.453809461549091</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.330534516960029</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0566137799747208</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-1.42931800555199</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-1.88560428652451</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.329698248715912</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.61140868840673</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.16122851479221</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.805163094109099</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.680849255122757</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.496902413392389</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.486452274317284</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.185437230637701</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.593050220991513</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.0395050789312107</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-1.83807651438127</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.974654998385597</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.626568643465774</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1.05726988508736</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.499820350108656</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.365558043305949</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.569927174806115</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.09166804998482</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.435012699418544</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.0196176533900736</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.711651842035909</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.314811222213512</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.265745320370446</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-1.09354214158336</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.0482436525164</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1.14517396740148</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.943062805339181</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.48924912049229</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.300157546657353</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.619833676476188</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.497794749945924</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-1.09944905835444</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.27560514664295</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.115964569371365</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.788309551549026</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.887799721960577</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.284850932598363</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.594236712578854</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.35881551389915</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.416567271491396</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.66163254426223</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.182174182947453</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.620072559870753</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.44226567838723</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.493319831179686</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.134227865020709</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.25862304949743</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.739676641142691</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.00429217482737432</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.937983328956385</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-1.28626077480009</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-4.18120889523023</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.33904147630253</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.710512787712842</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.100298138415243</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.560205908827036</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.459872108987991</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.228635363621834</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.316582732654377</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-1.25740511798621</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.40468959364291</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.799694206425194</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.660382066915406</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.723205571820559</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.74477159666732</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-1.09479071749834</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.0978854588802</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.208277019362284</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.0846349428604003</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.936281809304317</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1.30548738829665</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.29441379985431</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.801043238220909</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.352502486431549</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.125856784890868</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.49827175951382</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.0695389045511959</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.400428416749113</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.67864904440863</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.599945674731234</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.613335853697089</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.37318295964457</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.78905359180001</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.380701283798049</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-1.6139435806556</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-1.7853655067729</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.349245945503978</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.104297114306353</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-1.38027145638649</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.752881794440212</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.309159983997996</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.686765715548529</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.384638283595555</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.795781206712013</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.323001770018212</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.62497565197042</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.446704161822816</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.826583148040952</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.463308966624532</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.773710394057906</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.45745035521884</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.685282721370482</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.63753915499307</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.219007659541542</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-1.42059477589895</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.864451222574475</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.572979483283089</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.168630353449352</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.906652158035075</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.140233791752868</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.25252895487413</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.933590182677448</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.439733725150071</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1.35529883917024</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1.02673192895261</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.0475918598214813</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.33197407617332</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.976104768685944</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.28397473042198</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.300895667812869</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.370923968054457</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-1.73003600937261</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.102817467873168</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.8044491731986</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.349638984575455</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.278209517450438</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.215996956362836</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1.78311189227714</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.382961756907645</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.193545811745179</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-1.50577583643872</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.460468372556559</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.196677717285113</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.93548460100118</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.794377123903773</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.579371416170426</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.488592429886525</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-1.37436559453711</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.0031561898539676</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-1.08598924647902</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-1.0129281619011</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.80098003795747</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.809838422791954</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-2.19640891710862</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.492456840783208</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.462327268308223</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
